--- a/diseases/d013/2010-2014.xlsx
+++ b/diseases/d013/2010-2014.xlsx
@@ -21734,7 +21734,7 @@
       </c>
       <c r="AJ141" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK141" t="inlineStr">
@@ -22136,7 +22136,7 @@
       </c>
       <c r="AJ143" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK143" t="inlineStr">
@@ -22538,7 +22538,7 @@
       </c>
       <c r="AJ145" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK145" t="inlineStr">
@@ -23532,7 +23532,7 @@
       </c>
       <c r="AJ151" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK151" t="inlineStr">
@@ -23934,7 +23934,7 @@
       </c>
       <c r="AJ153" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK153" t="inlineStr">
@@ -24336,7 +24336,7 @@
       </c>
       <c r="AJ155" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK155" t="inlineStr">
@@ -24738,7 +24738,7 @@
       </c>
       <c r="AJ157" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK157" t="inlineStr">
@@ -25732,7 +25732,7 @@
       </c>
       <c r="AJ163" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK163" t="inlineStr">
@@ -26134,7 +26134,7 @@
       </c>
       <c r="AJ165" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK165" t="inlineStr">
@@ -26536,7 +26536,7 @@
       </c>
       <c r="AJ167" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK167" t="inlineStr">
@@ -26938,7 +26938,7 @@
       </c>
       <c r="AJ169" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK169" t="inlineStr">
@@ -27932,7 +27932,7 @@
       </c>
       <c r="AJ175" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK175" t="inlineStr">
@@ -28334,7 +28334,7 @@
       </c>
       <c r="AJ177" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK177" t="inlineStr">
@@ -28736,7 +28736,7 @@
       </c>
       <c r="AJ179" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK179" t="inlineStr">
@@ -29138,7 +29138,7 @@
       </c>
       <c r="AJ181" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK181" t="inlineStr">
@@ -29540,7 +29540,7 @@
       </c>
       <c r="AJ183" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK183" t="inlineStr">
@@ -30930,7 +30930,7 @@
       </c>
       <c r="AJ191" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK191" t="inlineStr">
@@ -31332,7 +31332,7 @@
       </c>
       <c r="AJ193" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK193" t="inlineStr">
@@ -31734,7 +31734,7 @@
       </c>
       <c r="AJ195" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK195" t="inlineStr">
@@ -32136,7 +32136,7 @@
       </c>
       <c r="AJ197" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK197" t="inlineStr">
@@ -33130,7 +33130,7 @@
       </c>
       <c r="AJ203" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK203" t="inlineStr">
@@ -33532,7 +33532,7 @@
       </c>
       <c r="AJ205" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK205" t="inlineStr">
@@ -33934,7 +33934,7 @@
       </c>
       <c r="AJ207" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK207" t="inlineStr">
@@ -34336,7 +34336,7 @@
       </c>
       <c r="AJ209" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK209" t="inlineStr">
@@ -35330,7 +35330,7 @@
       </c>
       <c r="AJ215" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK215" t="inlineStr">
@@ -35732,7 +35732,7 @@
       </c>
       <c r="AJ217" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK217" t="inlineStr">
@@ -36134,7 +36134,7 @@
       </c>
       <c r="AJ219" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK219" t="inlineStr">
@@ -36536,7 +36536,7 @@
       </c>
       <c r="AJ221" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK221" t="inlineStr">
@@ -36938,7 +36938,7 @@
       </c>
       <c r="AJ223" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK223" t="inlineStr">
@@ -37932,7 +37932,7 @@
       </c>
       <c r="AJ229" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK229" t="inlineStr">
@@ -38334,7 +38334,7 @@
       </c>
       <c r="AJ231" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK231" t="inlineStr">
@@ -38736,7 +38736,7 @@
       </c>
       <c r="AJ233" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK233" t="inlineStr">
@@ -39138,7 +39138,7 @@
       </c>
       <c r="AJ235" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK235" t="inlineStr">
@@ -40132,7 +40132,7 @@
       </c>
       <c r="AJ241" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK241" t="inlineStr">
@@ -40534,7 +40534,7 @@
       </c>
       <c r="AJ243" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK243" t="inlineStr">
@@ -40936,7 +40936,7 @@
       </c>
       <c r="AJ245" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK245" t="inlineStr">
@@ -41338,7 +41338,7 @@
       </c>
       <c r="AJ247" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK247" t="inlineStr">
@@ -42332,7 +42332,7 @@
       </c>
       <c r="AJ253" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK253" t="inlineStr">
@@ -42734,7 +42734,7 @@
       </c>
       <c r="AJ255" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK255" t="inlineStr">
@@ -43136,7 +43136,7 @@
       </c>
       <c r="AJ257" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK257" t="inlineStr">
@@ -43538,7 +43538,7 @@
       </c>
       <c r="AJ259" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK259" t="inlineStr">
@@ -43940,7 +43940,7 @@
       </c>
       <c r="AJ261" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK261" t="inlineStr">
@@ -44934,7 +44934,7 @@
       </c>
       <c r="AJ267" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK267" t="inlineStr">
@@ -45336,7 +45336,7 @@
       </c>
       <c r="AJ269" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK269" t="inlineStr">
@@ -45738,7 +45738,7 @@
       </c>
       <c r="AJ271" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK271" t="inlineStr">
@@ -46140,7 +46140,7 @@
       </c>
       <c r="AJ273" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK273" t="inlineStr">
@@ -47134,7 +47134,7 @@
       </c>
       <c r="AJ279" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK279" t="inlineStr">
@@ -47536,7 +47536,7 @@
       </c>
       <c r="AJ281" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK281" t="inlineStr">
@@ -47938,7 +47938,7 @@
       </c>
       <c r="AJ283" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK283" t="inlineStr">
@@ -48340,7 +48340,7 @@
       </c>
       <c r="AJ285" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK285" t="inlineStr">
@@ -49186,7 +49186,7 @@
       </c>
       <c r="AJ290" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK290" t="inlineStr">
@@ -49736,7 +49736,7 @@
       </c>
       <c r="AJ293" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK293" t="inlineStr">
@@ -50138,7 +50138,7 @@
       </c>
       <c r="AJ295" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK295" t="inlineStr">
@@ -50540,7 +50540,7 @@
       </c>
       <c r="AJ297" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK297" t="inlineStr">
@@ -50942,7 +50942,7 @@
       </c>
       <c r="AJ299" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK299" t="inlineStr">
@@ -51936,7 +51936,7 @@
       </c>
       <c r="AJ305" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK305" t="inlineStr">
@@ -52338,7 +52338,7 @@
       </c>
       <c r="AJ307" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK307" t="inlineStr">
@@ -52740,7 +52740,7 @@
       </c>
       <c r="AJ309" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK309" t="inlineStr">
@@ -53142,7 +53142,7 @@
       </c>
       <c r="AJ311" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK311" t="inlineStr">
@@ -54136,7 +54136,7 @@
       </c>
       <c r="AJ317" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK317" t="inlineStr">
@@ -54538,7 +54538,7 @@
       </c>
       <c r="AJ319" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK319" t="inlineStr">
@@ -54940,7 +54940,7 @@
       </c>
       <c r="AJ321" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK321" t="inlineStr">
@@ -55342,7 +55342,7 @@
       </c>
       <c r="AJ323" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK323" t="inlineStr">
@@ -56188,7 +56188,7 @@
       </c>
       <c r="AJ328" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK328" t="inlineStr">
@@ -56738,7 +56738,7 @@
       </c>
       <c r="AJ331" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK331" t="inlineStr">
@@ -57140,7 +57140,7 @@
       </c>
       <c r="AJ333" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK333" t="inlineStr">
@@ -57542,7 +57542,7 @@
       </c>
       <c r="AJ335" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK335" t="inlineStr">
@@ -57944,7 +57944,7 @@
       </c>
       <c r="AJ337" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK337" t="inlineStr">
@@ -59334,7 +59334,7 @@
       </c>
       <c r="AJ345" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK345" t="inlineStr">
@@ -59736,7 +59736,7 @@
       </c>
       <c r="AJ347" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK347" t="inlineStr">
@@ -60138,7 +60138,7 @@
       </c>
       <c r="AJ349" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK349" t="inlineStr">
@@ -60540,7 +60540,7 @@
       </c>
       <c r="AJ351" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK351" t="inlineStr">
@@ -61534,7 +61534,7 @@
       </c>
       <c r="AJ357" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK357" t="inlineStr">
@@ -61936,7 +61936,7 @@
       </c>
       <c r="AJ359" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK359" t="inlineStr">
@@ -62338,7 +62338,7 @@
       </c>
       <c r="AJ361" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK361" t="inlineStr">
@@ -62740,7 +62740,7 @@
       </c>
       <c r="AJ363" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK363" t="inlineStr">
@@ -63734,7 +63734,7 @@
       </c>
       <c r="AJ369" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK369" t="inlineStr">
@@ -64136,7 +64136,7 @@
       </c>
       <c r="AJ371" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK371" t="inlineStr">
@@ -64538,7 +64538,7 @@
       </c>
       <c r="AJ373" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK373" t="inlineStr">
@@ -64940,7 +64940,7 @@
       </c>
       <c r="AJ375" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK375" t="inlineStr">
@@ -65342,7 +65342,7 @@
       </c>
       <c r="AJ377" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK377" t="inlineStr">
@@ -66336,7 +66336,7 @@
       </c>
       <c r="AJ383" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK383" t="inlineStr">
@@ -66738,7 +66738,7 @@
       </c>
       <c r="AJ385" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK385" t="inlineStr">
@@ -67140,7 +67140,7 @@
       </c>
       <c r="AJ387" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK387" t="inlineStr">
@@ -67542,7 +67542,7 @@
       </c>
       <c r="AJ389" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK389" t="inlineStr">
@@ -68536,7 +68536,7 @@
       </c>
       <c r="AJ395" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK395" t="inlineStr">
@@ -68938,7 +68938,7 @@
       </c>
       <c r="AJ397" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK397" t="inlineStr">
@@ -69340,7 +69340,7 @@
       </c>
       <c r="AJ399" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK399" t="inlineStr">
@@ -69742,7 +69742,7 @@
       </c>
       <c r="AJ401" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK401" t="inlineStr">
@@ -70588,7 +70588,7 @@
       </c>
       <c r="AJ406" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK406" t="inlineStr">
@@ -71138,7 +71138,7 @@
       </c>
       <c r="AJ409" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK409" t="inlineStr">
@@ -71540,7 +71540,7 @@
       </c>
       <c r="AJ411" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK411" t="inlineStr">
@@ -71942,7 +71942,7 @@
       </c>
       <c r="AJ413" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK413" t="inlineStr">
@@ -72344,7 +72344,7 @@
       </c>
       <c r="AJ415" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK415" t="inlineStr">
@@ -73338,7 +73338,7 @@
       </c>
       <c r="AJ421" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK421" t="inlineStr">
@@ -73740,7 +73740,7 @@
       </c>
       <c r="AJ423" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK423" t="inlineStr">
@@ -74142,7 +74142,7 @@
       </c>
       <c r="AJ425" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK425" t="inlineStr">
@@ -74544,7 +74544,7 @@
       </c>
       <c r="AJ427" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK427" t="inlineStr">
@@ -75538,7 +75538,7 @@
       </c>
       <c r="AJ433" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK433" t="inlineStr">
@@ -75940,7 +75940,7 @@
       </c>
       <c r="AJ435" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK435" t="inlineStr">
@@ -76342,7 +76342,7 @@
       </c>
       <c r="AJ437" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK437" t="inlineStr">
@@ -76744,7 +76744,7 @@
       </c>
       <c r="AJ439" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK439" t="inlineStr">
@@ -77146,7 +77146,7 @@
       </c>
       <c r="AJ441" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK441" t="inlineStr">
@@ -78140,7 +78140,7 @@
       </c>
       <c r="AJ447" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK447" t="inlineStr">
@@ -78542,7 +78542,7 @@
       </c>
       <c r="AJ449" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK449" t="inlineStr">
@@ -78944,7 +78944,7 @@
       </c>
       <c r="AJ451" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK451" t="inlineStr">
@@ -79346,7 +79346,7 @@
       </c>
       <c r="AJ453" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK453" t="inlineStr">
@@ -80340,7 +80340,7 @@
       </c>
       <c r="AJ459" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK459" t="inlineStr">
@@ -80742,7 +80742,7 @@
       </c>
       <c r="AJ461" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK461" t="inlineStr">
@@ -81144,7 +81144,7 @@
       </c>
       <c r="AJ463" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK463" t="inlineStr">
@@ -81546,7 +81546,7 @@
       </c>
       <c r="AJ465" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK465" t="inlineStr">
@@ -82540,7 +82540,7 @@
       </c>
       <c r="AJ471" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK471" t="inlineStr">
@@ -82942,7 +82942,7 @@
       </c>
       <c r="AJ473" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK473" t="inlineStr">
@@ -83344,7 +83344,7 @@
       </c>
       <c r="AJ475" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK475" t="inlineStr">
@@ -83746,7 +83746,7 @@
       </c>
       <c r="AJ477" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK477" t="inlineStr">
@@ -84148,7 +84148,7 @@
       </c>
       <c r="AJ479" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK479" t="inlineStr">
@@ -85142,7 +85142,7 @@
       </c>
       <c r="AJ485" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK485" t="inlineStr">
@@ -85544,7 +85544,7 @@
       </c>
       <c r="AJ487" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK487" t="inlineStr">
@@ -85946,7 +85946,7 @@
       </c>
       <c r="AJ489" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK489" t="inlineStr">
@@ -86348,7 +86348,7 @@
       </c>
       <c r="AJ491" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK491" t="inlineStr">

--- a/diseases/d013/2010-2014.xlsx
+++ b/diseases/d013/2010-2014.xlsx
@@ -21734,7 +21734,7 @@
       </c>
       <c r="AJ141" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK141" t="inlineStr">
@@ -22136,7 +22136,7 @@
       </c>
       <c r="AJ143" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK143" t="inlineStr">
@@ -22538,7 +22538,7 @@
       </c>
       <c r="AJ145" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK145" t="inlineStr">
@@ -23532,7 +23532,7 @@
       </c>
       <c r="AJ151" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK151" t="inlineStr">
@@ -23934,7 +23934,7 @@
       </c>
       <c r="AJ153" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK153" t="inlineStr">
@@ -24336,7 +24336,7 @@
       </c>
       <c r="AJ155" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK155" t="inlineStr">
@@ -24738,7 +24738,7 @@
       </c>
       <c r="AJ157" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK157" t="inlineStr">
@@ -25732,7 +25732,7 @@
       </c>
       <c r="AJ163" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK163" t="inlineStr">
@@ -26134,7 +26134,7 @@
       </c>
       <c r="AJ165" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK165" t="inlineStr">
@@ -26536,7 +26536,7 @@
       </c>
       <c r="AJ167" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK167" t="inlineStr">
@@ -26938,7 +26938,7 @@
       </c>
       <c r="AJ169" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK169" t="inlineStr">
@@ -27932,7 +27932,7 @@
       </c>
       <c r="AJ175" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK175" t="inlineStr">
@@ -28334,7 +28334,7 @@
       </c>
       <c r="AJ177" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK177" t="inlineStr">
@@ -28736,7 +28736,7 @@
       </c>
       <c r="AJ179" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK179" t="inlineStr">
@@ -29138,7 +29138,7 @@
       </c>
       <c r="AJ181" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK181" t="inlineStr">
@@ -29540,7 +29540,7 @@
       </c>
       <c r="AJ183" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK183" t="inlineStr">
@@ -30930,7 +30930,7 @@
       </c>
       <c r="AJ191" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK191" t="inlineStr">
@@ -31332,7 +31332,7 @@
       </c>
       <c r="AJ193" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK193" t="inlineStr">
@@ -31734,7 +31734,7 @@
       </c>
       <c r="AJ195" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK195" t="inlineStr">
@@ -32136,7 +32136,7 @@
       </c>
       <c r="AJ197" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK197" t="inlineStr">
@@ -33130,7 +33130,7 @@
       </c>
       <c r="AJ203" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK203" t="inlineStr">
@@ -33532,7 +33532,7 @@
       </c>
       <c r="AJ205" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK205" t="inlineStr">
@@ -33934,7 +33934,7 @@
       </c>
       <c r="AJ207" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK207" t="inlineStr">
@@ -34336,7 +34336,7 @@
       </c>
       <c r="AJ209" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK209" t="inlineStr">
@@ -35330,7 +35330,7 @@
       </c>
       <c r="AJ215" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK215" t="inlineStr">
@@ -35732,7 +35732,7 @@
       </c>
       <c r="AJ217" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK217" t="inlineStr">
@@ -36134,7 +36134,7 @@
       </c>
       <c r="AJ219" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK219" t="inlineStr">
@@ -36536,7 +36536,7 @@
       </c>
       <c r="AJ221" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK221" t="inlineStr">
@@ -36938,7 +36938,7 @@
       </c>
       <c r="AJ223" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK223" t="inlineStr">
@@ -37932,7 +37932,7 @@
       </c>
       <c r="AJ229" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK229" t="inlineStr">
@@ -38334,7 +38334,7 @@
       </c>
       <c r="AJ231" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK231" t="inlineStr">
@@ -38736,7 +38736,7 @@
       </c>
       <c r="AJ233" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK233" t="inlineStr">
@@ -39138,7 +39138,7 @@
       </c>
       <c r="AJ235" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK235" t="inlineStr">
@@ -40132,7 +40132,7 @@
       </c>
       <c r="AJ241" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK241" t="inlineStr">
@@ -40534,7 +40534,7 @@
       </c>
       <c r="AJ243" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK243" t="inlineStr">
@@ -40936,7 +40936,7 @@
       </c>
       <c r="AJ245" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK245" t="inlineStr">
@@ -41338,7 +41338,7 @@
       </c>
       <c r="AJ247" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK247" t="inlineStr">
@@ -42332,7 +42332,7 @@
       </c>
       <c r="AJ253" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK253" t="inlineStr">
@@ -42734,7 +42734,7 @@
       </c>
       <c r="AJ255" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK255" t="inlineStr">
@@ -43136,7 +43136,7 @@
       </c>
       <c r="AJ257" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK257" t="inlineStr">
@@ -43538,7 +43538,7 @@
       </c>
       <c r="AJ259" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK259" t="inlineStr">
@@ -43940,7 +43940,7 @@
       </c>
       <c r="AJ261" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK261" t="inlineStr">
@@ -44934,7 +44934,7 @@
       </c>
       <c r="AJ267" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK267" t="inlineStr">
@@ -45336,7 +45336,7 @@
       </c>
       <c r="AJ269" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK269" t="inlineStr">
@@ -45738,7 +45738,7 @@
       </c>
       <c r="AJ271" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK271" t="inlineStr">
@@ -46140,7 +46140,7 @@
       </c>
       <c r="AJ273" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK273" t="inlineStr">
@@ -47134,7 +47134,7 @@
       </c>
       <c r="AJ279" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK279" t="inlineStr">
@@ -47536,7 +47536,7 @@
       </c>
       <c r="AJ281" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK281" t="inlineStr">
@@ -47938,7 +47938,7 @@
       </c>
       <c r="AJ283" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK283" t="inlineStr">
@@ -48340,7 +48340,7 @@
       </c>
       <c r="AJ285" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK285" t="inlineStr">
@@ -49186,7 +49186,7 @@
       </c>
       <c r="AJ290" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK290" t="inlineStr">
@@ -49736,7 +49736,7 @@
       </c>
       <c r="AJ293" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK293" t="inlineStr">
@@ -50138,7 +50138,7 @@
       </c>
       <c r="AJ295" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK295" t="inlineStr">
@@ -50540,7 +50540,7 @@
       </c>
       <c r="AJ297" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK297" t="inlineStr">
@@ -50942,7 +50942,7 @@
       </c>
       <c r="AJ299" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK299" t="inlineStr">
@@ -51936,7 +51936,7 @@
       </c>
       <c r="AJ305" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK305" t="inlineStr">
@@ -52338,7 +52338,7 @@
       </c>
       <c r="AJ307" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK307" t="inlineStr">
@@ -52740,7 +52740,7 @@
       </c>
       <c r="AJ309" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK309" t="inlineStr">
@@ -53142,7 +53142,7 @@
       </c>
       <c r="AJ311" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK311" t="inlineStr">
@@ -54136,7 +54136,7 @@
       </c>
       <c r="AJ317" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK317" t="inlineStr">
@@ -54538,7 +54538,7 @@
       </c>
       <c r="AJ319" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK319" t="inlineStr">
@@ -54940,7 +54940,7 @@
       </c>
       <c r="AJ321" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK321" t="inlineStr">
@@ -55342,7 +55342,7 @@
       </c>
       <c r="AJ323" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK323" t="inlineStr">
@@ -56188,7 +56188,7 @@
       </c>
       <c r="AJ328" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK328" t="inlineStr">
@@ -56738,7 +56738,7 @@
       </c>
       <c r="AJ331" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK331" t="inlineStr">
@@ -57140,7 +57140,7 @@
       </c>
       <c r="AJ333" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK333" t="inlineStr">
@@ -57542,7 +57542,7 @@
       </c>
       <c r="AJ335" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK335" t="inlineStr">
@@ -57944,7 +57944,7 @@
       </c>
       <c r="AJ337" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK337" t="inlineStr">
@@ -59334,7 +59334,7 @@
       </c>
       <c r="AJ345" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK345" t="inlineStr">
@@ -59736,7 +59736,7 @@
       </c>
       <c r="AJ347" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK347" t="inlineStr">
@@ -60138,7 +60138,7 @@
       </c>
       <c r="AJ349" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK349" t="inlineStr">
@@ -60540,7 +60540,7 @@
       </c>
       <c r="AJ351" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK351" t="inlineStr">
@@ -61534,7 +61534,7 @@
       </c>
       <c r="AJ357" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK357" t="inlineStr">
@@ -61936,7 +61936,7 @@
       </c>
       <c r="AJ359" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK359" t="inlineStr">
@@ -62338,7 +62338,7 @@
       </c>
       <c r="AJ361" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK361" t="inlineStr">
@@ -62740,7 +62740,7 @@
       </c>
       <c r="AJ363" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK363" t="inlineStr">
@@ -63734,7 +63734,7 @@
       </c>
       <c r="AJ369" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK369" t="inlineStr">
@@ -64136,7 +64136,7 @@
       </c>
       <c r="AJ371" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK371" t="inlineStr">
@@ -64538,7 +64538,7 @@
       </c>
       <c r="AJ373" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK373" t="inlineStr">
@@ -64940,7 +64940,7 @@
       </c>
       <c r="AJ375" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK375" t="inlineStr">
@@ -65342,7 +65342,7 @@
       </c>
       <c r="AJ377" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK377" t="inlineStr">
@@ -66336,7 +66336,7 @@
       </c>
       <c r="AJ383" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK383" t="inlineStr">
@@ -66738,7 +66738,7 @@
       </c>
       <c r="AJ385" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK385" t="inlineStr">
@@ -67140,7 +67140,7 @@
       </c>
       <c r="AJ387" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK387" t="inlineStr">
@@ -67542,7 +67542,7 @@
       </c>
       <c r="AJ389" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK389" t="inlineStr">
@@ -68536,7 +68536,7 @@
       </c>
       <c r="AJ395" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK395" t="inlineStr">
@@ -68938,7 +68938,7 @@
       </c>
       <c r="AJ397" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK397" t="inlineStr">
@@ -69340,7 +69340,7 @@
       </c>
       <c r="AJ399" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK399" t="inlineStr">
@@ -69742,7 +69742,7 @@
       </c>
       <c r="AJ401" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK401" t="inlineStr">
@@ -70588,7 +70588,7 @@
       </c>
       <c r="AJ406" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK406" t="inlineStr">
@@ -71138,7 +71138,7 @@
       </c>
       <c r="AJ409" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK409" t="inlineStr">
@@ -71540,7 +71540,7 @@
       </c>
       <c r="AJ411" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK411" t="inlineStr">
@@ -71942,7 +71942,7 @@
       </c>
       <c r="AJ413" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK413" t="inlineStr">
@@ -72344,7 +72344,7 @@
       </c>
       <c r="AJ415" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK415" t="inlineStr">
@@ -73338,7 +73338,7 @@
       </c>
       <c r="AJ421" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK421" t="inlineStr">
@@ -73740,7 +73740,7 @@
       </c>
       <c r="AJ423" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK423" t="inlineStr">
@@ -74142,7 +74142,7 @@
       </c>
       <c r="AJ425" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK425" t="inlineStr">
@@ -74544,7 +74544,7 @@
       </c>
       <c r="AJ427" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK427" t="inlineStr">
@@ -75538,7 +75538,7 @@
       </c>
       <c r="AJ433" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK433" t="inlineStr">
@@ -75940,7 +75940,7 @@
       </c>
       <c r="AJ435" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK435" t="inlineStr">
@@ -76342,7 +76342,7 @@
       </c>
       <c r="AJ437" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK437" t="inlineStr">
@@ -76744,7 +76744,7 @@
       </c>
       <c r="AJ439" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK439" t="inlineStr">
@@ -77146,7 +77146,7 @@
       </c>
       <c r="AJ441" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK441" t="inlineStr">
@@ -78140,7 +78140,7 @@
       </c>
       <c r="AJ447" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK447" t="inlineStr">
@@ -78542,7 +78542,7 @@
       </c>
       <c r="AJ449" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK449" t="inlineStr">
@@ -78944,7 +78944,7 @@
       </c>
       <c r="AJ451" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK451" t="inlineStr">
@@ -79346,7 +79346,7 @@
       </c>
       <c r="AJ453" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK453" t="inlineStr">
@@ -80340,7 +80340,7 @@
       </c>
       <c r="AJ459" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK459" t="inlineStr">
@@ -80742,7 +80742,7 @@
       </c>
       <c r="AJ461" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK461" t="inlineStr">
@@ -81144,7 +81144,7 @@
       </c>
       <c r="AJ463" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK463" t="inlineStr">
@@ -81546,7 +81546,7 @@
       </c>
       <c r="AJ465" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK465" t="inlineStr">
@@ -82540,7 +82540,7 @@
       </c>
       <c r="AJ471" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK471" t="inlineStr">
@@ -82942,7 +82942,7 @@
       </c>
       <c r="AJ473" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK473" t="inlineStr">
@@ -83344,7 +83344,7 @@
       </c>
       <c r="AJ475" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK475" t="inlineStr">
@@ -83746,7 +83746,7 @@
       </c>
       <c r="AJ477" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK477" t="inlineStr">
@@ -84148,7 +84148,7 @@
       </c>
       <c r="AJ479" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK479" t="inlineStr">
@@ -85142,7 +85142,7 @@
       </c>
       <c r="AJ485" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK485" t="inlineStr">
@@ -85544,7 +85544,7 @@
       </c>
       <c r="AJ487" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK487" t="inlineStr">
@@ -85946,7 +85946,7 @@
       </c>
       <c r="AJ489" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK489" t="inlineStr">
@@ -86348,7 +86348,7 @@
       </c>
       <c r="AJ491" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK491" t="inlineStr">

--- a/diseases/d013/2010-2014.xlsx
+++ b/diseases/d013/2010-2014.xlsx
@@ -1209,9 +1209,6 @@
       <c r="O5" t="n">
         <v>0</v>
       </c>
-      <c r="Q5" t="n">
-        <v>0</v>
-      </c>
       <c r="R5" t="n">
         <v>0</v>
       </c>
@@ -1605,9 +1602,6 @@
       <c r="O7" t="n">
         <v>0</v>
       </c>
-      <c r="Q7" t="n">
-        <v>0</v>
-      </c>
       <c r="R7" t="n">
         <v>0</v>
       </c>
@@ -2197,9 +2191,6 @@
       <c r="O11" t="n">
         <v>0</v>
       </c>
-      <c r="Q11" t="n">
-        <v>0</v>
-      </c>
       <c r="R11" t="n">
         <v>0</v>
       </c>
@@ -2789,9 +2780,6 @@
       <c r="O15" t="n">
         <v>0</v>
       </c>
-      <c r="Q15" t="n">
-        <v>0</v>
-      </c>
       <c r="R15" t="n">
         <v>0</v>
       </c>
@@ -3381,9 +3369,6 @@
       <c r="O19" t="n">
         <v>0</v>
       </c>
-      <c r="Q19" t="n">
-        <v>0</v>
-      </c>
       <c r="R19" t="n">
         <v>0</v>
       </c>
@@ -3973,9 +3958,6 @@
       <c r="O23" t="n">
         <v>0</v>
       </c>
-      <c r="Q23" t="n">
-        <v>0</v>
-      </c>
       <c r="R23" t="n">
         <v>0</v>
       </c>
@@ -4565,9 +4547,6 @@
       <c r="O27" t="n">
         <v>0</v>
       </c>
-      <c r="Q27" t="n">
-        <v>0</v>
-      </c>
       <c r="R27" t="n">
         <v>0</v>
       </c>
@@ -5157,9 +5136,6 @@
       <c r="O31" t="n">
         <v>0</v>
       </c>
-      <c r="Q31" t="n">
-        <v>0</v>
-      </c>
       <c r="R31" t="n">
         <v>0</v>
       </c>
@@ -5749,9 +5725,6 @@
       <c r="O35" t="n">
         <v>0</v>
       </c>
-      <c r="Q35" t="n">
-        <v>0</v>
-      </c>
       <c r="R35" t="n">
         <v>0</v>
       </c>
@@ -6341,9 +6314,6 @@
       <c r="O39" t="n">
         <v>0</v>
       </c>
-      <c r="Q39" t="n">
-        <v>0</v>
-      </c>
       <c r="R39" t="n">
         <v>0</v>
       </c>
@@ -6933,9 +6903,6 @@
       <c r="O43" t="n">
         <v>0</v>
       </c>
-      <c r="Q43" t="n">
-        <v>0</v>
-      </c>
       <c r="R43" t="n">
         <v>0</v>
       </c>
@@ -7525,9 +7492,6 @@
       <c r="O47" t="n">
         <v>0</v>
       </c>
-      <c r="Q47" t="n">
-        <v>0</v>
-      </c>
       <c r="R47" t="n">
         <v>0</v>
       </c>
@@ -8117,9 +8081,6 @@
       <c r="O51" t="n">
         <v>0</v>
       </c>
-      <c r="Q51" t="n">
-        <v>0</v>
-      </c>
       <c r="R51" t="n">
         <v>0</v>
       </c>
@@ -8709,9 +8670,6 @@
       <c r="O55" t="n">
         <v>0</v>
       </c>
-      <c r="Q55" t="n">
-        <v>0</v>
-      </c>
       <c r="R55" t="n">
         <v>0</v>
       </c>
@@ -9105,9 +9063,6 @@
       <c r="O57" t="n">
         <v>0</v>
       </c>
-      <c r="Q57" t="n">
-        <v>0</v>
-      </c>
       <c r="R57" t="n">
         <v>0</v>
       </c>
@@ -9697,9 +9652,6 @@
       <c r="O61" t="n">
         <v>0</v>
       </c>
-      <c r="Q61" t="n">
-        <v>0</v>
-      </c>
       <c r="R61" t="n">
         <v>0</v>
       </c>
@@ -10289,9 +10241,6 @@
       <c r="O65" t="n">
         <v>0</v>
       </c>
-      <c r="Q65" t="n">
-        <v>0</v>
-      </c>
       <c r="R65" t="n">
         <v>0</v>
       </c>
@@ -10881,9 +10830,6 @@
       <c r="O69" t="n">
         <v>0</v>
       </c>
-      <c r="Q69" t="n">
-        <v>0</v>
-      </c>
       <c r="R69" t="n">
         <v>0</v>
       </c>
@@ -11473,9 +11419,6 @@
       <c r="O73" t="n">
         <v>0</v>
       </c>
-      <c r="Q73" t="n">
-        <v>0</v>
-      </c>
       <c r="R73" t="n">
         <v>0</v>
       </c>
@@ -12065,9 +12008,6 @@
       <c r="O77" t="n">
         <v>0</v>
       </c>
-      <c r="Q77" t="n">
-        <v>0</v>
-      </c>
       <c r="R77" t="n">
         <v>0</v>
       </c>
@@ -12657,9 +12597,6 @@
       <c r="O81" t="n">
         <v>0</v>
       </c>
-      <c r="Q81" t="n">
-        <v>0</v>
-      </c>
       <c r="R81" t="n">
         <v>0</v>
       </c>
@@ -13249,9 +13186,6 @@
       <c r="O85" t="n">
         <v>0</v>
       </c>
-      <c r="Q85" t="n">
-        <v>0</v>
-      </c>
       <c r="R85" t="n">
         <v>0</v>
       </c>
@@ -13841,9 +13775,6 @@
       <c r="O89" t="n">
         <v>0</v>
       </c>
-      <c r="Q89" t="n">
-        <v>0</v>
-      </c>
       <c r="R89" t="n">
         <v>0</v>
       </c>
@@ -14433,9 +14364,6 @@
       <c r="O93" t="n">
         <v>0</v>
       </c>
-      <c r="Q93" t="n">
-        <v>0</v>
-      </c>
       <c r="R93" t="n">
         <v>0</v>
       </c>
@@ -15025,9 +14953,6 @@
       <c r="O97" t="n">
         <v>0</v>
       </c>
-      <c r="Q97" t="n">
-        <v>0</v>
-      </c>
       <c r="R97" t="n">
         <v>0</v>
       </c>
@@ -15617,9 +15542,6 @@
       <c r="O101" t="n">
         <v>0</v>
       </c>
-      <c r="Q101" t="n">
-        <v>0</v>
-      </c>
       <c r="R101" t="n">
         <v>0</v>
       </c>
@@ -16209,9 +16131,6 @@
       <c r="O105" t="n">
         <v>0</v>
       </c>
-      <c r="Q105" t="n">
-        <v>0</v>
-      </c>
       <c r="R105" t="n">
         <v>0</v>
       </c>
@@ -16605,9 +16524,6 @@
       <c r="O107" t="n">
         <v>0</v>
       </c>
-      <c r="Q107" t="n">
-        <v>0</v>
-      </c>
       <c r="R107" t="n">
         <v>0</v>
       </c>
@@ -17197,9 +17113,6 @@
       <c r="O111" t="n">
         <v>0</v>
       </c>
-      <c r="Q111" t="n">
-        <v>0</v>
-      </c>
       <c r="R111" t="n">
         <v>0</v>
       </c>
@@ -17789,9 +17702,6 @@
       <c r="O115" t="n">
         <v>0</v>
       </c>
-      <c r="Q115" t="n">
-        <v>0</v>
-      </c>
       <c r="R115" t="n">
         <v>0</v>
       </c>
@@ -18381,9 +18291,6 @@
       <c r="O119" t="n">
         <v>0</v>
       </c>
-      <c r="Q119" t="n">
-        <v>0</v>
-      </c>
       <c r="R119" t="n">
         <v>0</v>
       </c>
@@ -18973,9 +18880,6 @@
       <c r="O123" t="n">
         <v>0</v>
       </c>
-      <c r="Q123" t="n">
-        <v>0</v>
-      </c>
       <c r="R123" t="n">
         <v>0</v>
       </c>
@@ -19565,9 +19469,6 @@
       <c r="O127" t="n">
         <v>0</v>
       </c>
-      <c r="Q127" t="n">
-        <v>0</v>
-      </c>
       <c r="R127" t="n">
         <v>0</v>
       </c>
@@ -20157,9 +20058,6 @@
       <c r="O131" t="n">
         <v>0</v>
       </c>
-      <c r="Q131" t="n">
-        <v>0</v>
-      </c>
       <c r="R131" t="n">
         <v>0</v>
       </c>
@@ -20749,9 +20647,6 @@
       <c r="O135" t="n">
         <v>0</v>
       </c>
-      <c r="Q135" t="n">
-        <v>0</v>
-      </c>
       <c r="R135" t="n">
         <v>0</v>
       </c>
@@ -21341,9 +21236,6 @@
       <c r="O139" t="n">
         <v>0</v>
       </c>
-      <c r="Q139" t="n">
-        <v>0</v>
-      </c>
       <c r="R139" t="n">
         <v>0</v>
       </c>
@@ -21744,7 +21636,7 @@
       </c>
       <c r="AM141" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN141" t="b">
@@ -22146,7 +22038,7 @@
       </c>
       <c r="AM143" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN143" t="b">
@@ -22548,7 +22440,7 @@
       </c>
       <c r="AM145" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN145" t="b">
@@ -23139,9 +23031,6 @@
       <c r="O149" t="n">
         <v>0</v>
       </c>
-      <c r="Q149" t="n">
-        <v>0</v>
-      </c>
       <c r="R149" t="n">
         <v>0</v>
       </c>
@@ -23542,7 +23431,7 @@
       </c>
       <c r="AM151" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN151" t="b">
@@ -23944,7 +23833,7 @@
       </c>
       <c r="AM153" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN153" t="b">
@@ -24346,7 +24235,7 @@
       </c>
       <c r="AM155" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN155" t="b">
@@ -24748,7 +24637,7 @@
       </c>
       <c r="AM157" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN157" t="b">
@@ -25339,9 +25228,6 @@
       <c r="O161" t="n">
         <v>0</v>
       </c>
-      <c r="Q161" t="n">
-        <v>0</v>
-      </c>
       <c r="R161" t="n">
         <v>0</v>
       </c>
@@ -25742,7 +25628,7 @@
       </c>
       <c r="AM163" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN163" t="b">
@@ -26144,7 +26030,7 @@
       </c>
       <c r="AM165" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN165" t="b">
@@ -26546,7 +26432,7 @@
       </c>
       <c r="AM167" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN167" t="b">
@@ -26948,7 +26834,7 @@
       </c>
       <c r="AM169" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN169" t="b">
@@ -27539,9 +27425,6 @@
       <c r="O173" t="n">
         <v>0</v>
       </c>
-      <c r="Q173" t="n">
-        <v>0</v>
-      </c>
       <c r="R173" t="n">
         <v>0</v>
       </c>
@@ -27942,7 +27825,7 @@
       </c>
       <c r="AM175" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN175" t="b">
@@ -28344,7 +28227,7 @@
       </c>
       <c r="AM177" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN177" t="b">
@@ -28746,7 +28629,7 @@
       </c>
       <c r="AM179" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN179" t="b">
@@ -29148,7 +29031,7 @@
       </c>
       <c r="AM181" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN181" t="b">
@@ -29550,7 +29433,7 @@
       </c>
       <c r="AM183" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN183" t="b">
@@ -30141,9 +30024,6 @@
       <c r="O187" t="n">
         <v>0</v>
       </c>
-      <c r="Q187" t="n">
-        <v>0</v>
-      </c>
       <c r="R187" t="n">
         <v>0</v>
       </c>
@@ -30537,9 +30417,6 @@
       <c r="O189" t="n">
         <v>0</v>
       </c>
-      <c r="Q189" t="n">
-        <v>0</v>
-      </c>
       <c r="R189" t="n">
         <v>0</v>
       </c>
@@ -30940,7 +30817,7 @@
       </c>
       <c r="AM191" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN191" t="b">
@@ -31342,7 +31219,7 @@
       </c>
       <c r="AM193" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN193" t="b">
@@ -31744,7 +31621,7 @@
       </c>
       <c r="AM195" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN195" t="b">
@@ -32146,7 +32023,7 @@
       </c>
       <c r="AM197" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN197" t="b">
@@ -32737,9 +32614,6 @@
       <c r="O201" t="n">
         <v>0</v>
       </c>
-      <c r="Q201" t="n">
-        <v>0</v>
-      </c>
       <c r="R201" t="n">
         <v>0</v>
       </c>
@@ -33140,7 +33014,7 @@
       </c>
       <c r="AM203" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN203" t="b">
@@ -33542,7 +33416,7 @@
       </c>
       <c r="AM205" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN205" t="b">
@@ -33944,7 +33818,7 @@
       </c>
       <c r="AM207" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN207" t="b">
@@ -34346,7 +34220,7 @@
       </c>
       <c r="AM209" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN209" t="b">
@@ -34937,9 +34811,6 @@
       <c r="O213" t="n">
         <v>0</v>
       </c>
-      <c r="Q213" t="n">
-        <v>0</v>
-      </c>
       <c r="R213" t="n">
         <v>0</v>
       </c>
@@ -35340,7 +35211,7 @@
       </c>
       <c r="AM215" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN215" t="b">
@@ -35742,7 +35613,7 @@
       </c>
       <c r="AM217" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN217" t="b">
@@ -36144,7 +36015,7 @@
       </c>
       <c r="AM219" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN219" t="b">
@@ -36546,7 +36417,7 @@
       </c>
       <c r="AM221" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN221" t="b">
@@ -36948,7 +36819,7 @@
       </c>
       <c r="AM223" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN223" t="b">
@@ -37539,9 +37410,6 @@
       <c r="O227" t="n">
         <v>0</v>
       </c>
-      <c r="Q227" t="n">
-        <v>0</v>
-      </c>
       <c r="R227" t="n">
         <v>0</v>
       </c>
@@ -37942,7 +37810,7 @@
       </c>
       <c r="AM229" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN229" t="b">
@@ -38344,7 +38212,7 @@
       </c>
       <c r="AM231" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN231" t="b">
@@ -38746,7 +38614,7 @@
       </c>
       <c r="AM233" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN233" t="b">
@@ -39148,7 +39016,7 @@
       </c>
       <c r="AM235" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN235" t="b">
@@ -39739,9 +39607,6 @@
       <c r="O239" t="n">
         <v>0</v>
       </c>
-      <c r="Q239" t="n">
-        <v>0</v>
-      </c>
       <c r="R239" t="n">
         <v>0</v>
       </c>
@@ -40142,7 +40007,7 @@
       </c>
       <c r="AM241" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN241" t="b">
@@ -40544,7 +40409,7 @@
       </c>
       <c r="AM243" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN243" t="b">
@@ -40946,7 +40811,7 @@
       </c>
       <c r="AM245" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN245" t="b">
@@ -41348,7 +41213,7 @@
       </c>
       <c r="AM247" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN247" t="b">
@@ -41939,9 +41804,6 @@
       <c r="O251" t="n">
         <v>0</v>
       </c>
-      <c r="Q251" t="n">
-        <v>0</v>
-      </c>
       <c r="R251" t="n">
         <v>0</v>
       </c>
@@ -42342,7 +42204,7 @@
       </c>
       <c r="AM253" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN253" t="b">
@@ -42744,7 +42606,7 @@
       </c>
       <c r="AM255" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN255" t="b">
@@ -43146,7 +43008,7 @@
       </c>
       <c r="AM257" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN257" t="b">
@@ -43548,7 +43410,7 @@
       </c>
       <c r="AM259" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN259" t="b">
@@ -43950,7 +43812,7 @@
       </c>
       <c r="AM261" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN261" t="b">
@@ -44541,9 +44403,6 @@
       <c r="O265" t="n">
         <v>0</v>
       </c>
-      <c r="Q265" t="n">
-        <v>0</v>
-      </c>
       <c r="R265" t="n">
         <v>0</v>
       </c>
@@ -44944,7 +44803,7 @@
       </c>
       <c r="AM267" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN267" t="b">
@@ -45346,7 +45205,7 @@
       </c>
       <c r="AM269" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN269" t="b">
@@ -45748,7 +45607,7 @@
       </c>
       <c r="AM271" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN271" t="b">
@@ -46150,7 +46009,7 @@
       </c>
       <c r="AM273" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN273" t="b">
@@ -46741,9 +46600,6 @@
       <c r="O277" t="n">
         <v>0</v>
       </c>
-      <c r="Q277" t="n">
-        <v>0</v>
-      </c>
       <c r="R277" t="n">
         <v>0</v>
       </c>
@@ -47144,7 +47000,7 @@
       </c>
       <c r="AM279" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN279" t="b">
@@ -47546,7 +47402,7 @@
       </c>
       <c r="AM281" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN281" t="b">
@@ -47948,7 +47804,7 @@
       </c>
       <c r="AM283" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN283" t="b">
@@ -48350,7 +48206,7 @@
       </c>
       <c r="AM285" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN285" t="b">
@@ -49196,7 +49052,7 @@
       </c>
       <c r="AM290" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN290" t="b">
@@ -49343,9 +49199,6 @@
       <c r="O291" t="n">
         <v>0</v>
       </c>
-      <c r="Q291" t="n">
-        <v>0</v>
-      </c>
       <c r="R291" t="n">
         <v>0</v>
       </c>
@@ -49746,7 +49599,7 @@
       </c>
       <c r="AM293" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN293" t="b">
@@ -50148,7 +50001,7 @@
       </c>
       <c r="AM295" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN295" t="b">
@@ -50550,7 +50403,7 @@
       </c>
       <c r="AM297" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN297" t="b">
@@ -50952,7 +50805,7 @@
       </c>
       <c r="AM299" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN299" t="b">
@@ -51543,9 +51396,6 @@
       <c r="O303" t="n">
         <v>0</v>
       </c>
-      <c r="Q303" t="n">
-        <v>0</v>
-      </c>
       <c r="R303" t="n">
         <v>0</v>
       </c>
@@ -51946,7 +51796,7 @@
       </c>
       <c r="AM305" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN305" t="b">
@@ -52348,7 +52198,7 @@
       </c>
       <c r="AM307" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN307" t="b">
@@ -52750,7 +52600,7 @@
       </c>
       <c r="AM309" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN309" t="b">
@@ -53152,7 +53002,7 @@
       </c>
       <c r="AM311" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN311" t="b">
@@ -53743,9 +53593,6 @@
       <c r="O315" t="n">
         <v>0</v>
       </c>
-      <c r="Q315" t="n">
-        <v>0</v>
-      </c>
       <c r="R315" t="n">
         <v>0</v>
       </c>
@@ -54146,7 +53993,7 @@
       </c>
       <c r="AM317" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN317" t="b">
@@ -54548,7 +54395,7 @@
       </c>
       <c r="AM319" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN319" t="b">
@@ -54950,7 +54797,7 @@
       </c>
       <c r="AM321" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN321" t="b">
@@ -55352,7 +55199,7 @@
       </c>
       <c r="AM323" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN323" t="b">
@@ -56198,7 +56045,7 @@
       </c>
       <c r="AM328" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN328" t="b">
@@ -56345,9 +56192,6 @@
       <c r="O329" t="n">
         <v>0</v>
       </c>
-      <c r="Q329" t="n">
-        <v>0</v>
-      </c>
       <c r="R329" t="n">
         <v>0</v>
       </c>
@@ -56748,7 +56592,7 @@
       </c>
       <c r="AM331" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN331" t="b">
@@ -57150,7 +56994,7 @@
       </c>
       <c r="AM333" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN333" t="b">
@@ -57552,7 +57396,7 @@
       </c>
       <c r="AM335" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN335" t="b">
@@ -57954,7 +57798,7 @@
       </c>
       <c r="AM337" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN337" t="b">
@@ -58545,9 +58389,6 @@
       <c r="O341" t="n">
         <v>0</v>
       </c>
-      <c r="Q341" t="n">
-        <v>0</v>
-      </c>
       <c r="R341" t="n">
         <v>0</v>
       </c>
@@ -58941,9 +58782,6 @@
       <c r="O343" t="n">
         <v>0</v>
       </c>
-      <c r="Q343" t="n">
-        <v>0</v>
-      </c>
       <c r="R343" t="n">
         <v>0</v>
       </c>
@@ -59344,7 +59182,7 @@
       </c>
       <c r="AM345" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN345" t="b">
@@ -59746,7 +59584,7 @@
       </c>
       <c r="AM347" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN347" t="b">
@@ -60148,7 +59986,7 @@
       </c>
       <c r="AM349" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN349" t="b">
@@ -60550,7 +60388,7 @@
       </c>
       <c r="AM351" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN351" t="b">
@@ -61141,9 +60979,6 @@
       <c r="O355" t="n">
         <v>0</v>
       </c>
-      <c r="Q355" t="n">
-        <v>0</v>
-      </c>
       <c r="R355" t="n">
         <v>0</v>
       </c>
@@ -61544,7 +61379,7 @@
       </c>
       <c r="AM357" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN357" t="b">
@@ -61946,7 +61781,7 @@
       </c>
       <c r="AM359" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN359" t="b">
@@ -62348,7 +62183,7 @@
       </c>
       <c r="AM361" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN361" t="b">
@@ -62750,7 +62585,7 @@
       </c>
       <c r="AM363" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN363" t="b">
@@ -63341,9 +63176,6 @@
       <c r="O367" t="n">
         <v>0</v>
       </c>
-      <c r="Q367" t="n">
-        <v>0</v>
-      </c>
       <c r="R367" t="n">
         <v>0</v>
       </c>
@@ -63744,7 +63576,7 @@
       </c>
       <c r="AM369" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN369" t="b">
@@ -64146,7 +63978,7 @@
       </c>
       <c r="AM371" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN371" t="b">
@@ -64548,7 +64380,7 @@
       </c>
       <c r="AM373" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN373" t="b">
@@ -64950,7 +64782,7 @@
       </c>
       <c r="AM375" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN375" t="b">
@@ -65352,7 +65184,7 @@
       </c>
       <c r="AM377" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN377" t="b">
@@ -65943,9 +65775,6 @@
       <c r="O381" t="n">
         <v>0</v>
       </c>
-      <c r="Q381" t="n">
-        <v>0</v>
-      </c>
       <c r="R381" t="n">
         <v>0</v>
       </c>
@@ -66346,7 +66175,7 @@
       </c>
       <c r="AM383" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN383" t="b">
@@ -66748,7 +66577,7 @@
       </c>
       <c r="AM385" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN385" t="b">
@@ -67150,7 +66979,7 @@
       </c>
       <c r="AM387" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN387" t="b">
@@ -67552,7 +67381,7 @@
       </c>
       <c r="AM389" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN389" t="b">
@@ -68143,9 +67972,6 @@
       <c r="O393" t="n">
         <v>0</v>
       </c>
-      <c r="Q393" t="n">
-        <v>0</v>
-      </c>
       <c r="R393" t="n">
         <v>0</v>
       </c>
@@ -68546,7 +68372,7 @@
       </c>
       <c r="AM395" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN395" t="b">
@@ -68948,7 +68774,7 @@
       </c>
       <c r="AM397" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN397" t="b">
@@ -69350,7 +69176,7 @@
       </c>
       <c r="AM399" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN399" t="b">
@@ -69752,7 +69578,7 @@
       </c>
       <c r="AM401" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN401" t="b">
@@ -70598,7 +70424,7 @@
       </c>
       <c r="AM406" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN406" t="b">
@@ -70745,9 +70571,6 @@
       <c r="O407" t="n">
         <v>0</v>
       </c>
-      <c r="Q407" t="n">
-        <v>0</v>
-      </c>
       <c r="R407" t="n">
         <v>0</v>
       </c>
@@ -71148,7 +70971,7 @@
       </c>
       <c r="AM409" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN409" t="b">
@@ -71550,7 +71373,7 @@
       </c>
       <c r="AM411" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN411" t="b">
@@ -71952,7 +71775,7 @@
       </c>
       <c r="AM413" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN413" t="b">
@@ -72354,7 +72177,7 @@
       </c>
       <c r="AM415" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN415" t="b">
@@ -72945,9 +72768,6 @@
       <c r="O419" t="n">
         <v>0</v>
       </c>
-      <c r="Q419" t="n">
-        <v>0</v>
-      </c>
       <c r="R419" t="n">
         <v>0</v>
       </c>
@@ -73348,7 +73168,7 @@
       </c>
       <c r="AM421" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN421" t="b">
@@ -73750,7 +73570,7 @@
       </c>
       <c r="AM423" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN423" t="b">
@@ -74152,7 +73972,7 @@
       </c>
       <c r="AM425" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN425" t="b">
@@ -74554,7 +74374,7 @@
       </c>
       <c r="AM427" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN427" t="b">
@@ -75145,9 +74965,6 @@
       <c r="O431" t="n">
         <v>0</v>
       </c>
-      <c r="Q431" t="n">
-        <v>0</v>
-      </c>
       <c r="R431" t="n">
         <v>0</v>
       </c>
@@ -75548,7 +75365,7 @@
       </c>
       <c r="AM433" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN433" t="b">
@@ -75950,7 +75767,7 @@
       </c>
       <c r="AM435" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN435" t="b">
@@ -76352,7 +76169,7 @@
       </c>
       <c r="AM437" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN437" t="b">
@@ -76754,7 +76571,7 @@
       </c>
       <c r="AM439" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN439" t="b">
@@ -77156,7 +76973,7 @@
       </c>
       <c r="AM441" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN441" t="b">
@@ -77747,9 +77564,6 @@
       <c r="O445" t="n">
         <v>0</v>
       </c>
-      <c r="Q445" t="n">
-        <v>0</v>
-      </c>
       <c r="R445" t="n">
         <v>0</v>
       </c>
@@ -78150,7 +77964,7 @@
       </c>
       <c r="AM447" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN447" t="b">
@@ -78552,7 +78366,7 @@
       </c>
       <c r="AM449" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN449" t="b">
@@ -78954,7 +78768,7 @@
       </c>
       <c r="AM451" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN451" t="b">
@@ -79356,7 +79170,7 @@
       </c>
       <c r="AM453" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN453" t="b">
@@ -79947,9 +79761,6 @@
       <c r="O457" t="n">
         <v>0</v>
       </c>
-      <c r="Q457" t="n">
-        <v>0</v>
-      </c>
       <c r="R457" t="n">
         <v>0</v>
       </c>
@@ -80350,7 +80161,7 @@
       </c>
       <c r="AM459" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN459" t="b">
@@ -80752,7 +80563,7 @@
       </c>
       <c r="AM461" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN461" t="b">
@@ -81154,7 +80965,7 @@
       </c>
       <c r="AM463" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN463" t="b">
@@ -81556,7 +81367,7 @@
       </c>
       <c r="AM465" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN465" t="b">
@@ -82147,9 +81958,6 @@
       <c r="O469" t="n">
         <v>0</v>
       </c>
-      <c r="Q469" t="n">
-        <v>0</v>
-      </c>
       <c r="R469" t="n">
         <v>0</v>
       </c>
@@ -82550,7 +82358,7 @@
       </c>
       <c r="AM471" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN471" t="b">
@@ -82952,7 +82760,7 @@
       </c>
       <c r="AM473" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN473" t="b">
@@ -83354,7 +83162,7 @@
       </c>
       <c r="AM475" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN475" t="b">
@@ -83756,7 +83564,7 @@
       </c>
       <c r="AM477" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN477" t="b">
@@ -84158,7 +83966,7 @@
       </c>
       <c r="AM479" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN479" t="b">
@@ -84749,9 +84557,6 @@
       <c r="O483" t="n">
         <v>0</v>
       </c>
-      <c r="Q483" t="n">
-        <v>0</v>
-      </c>
       <c r="R483" t="n">
         <v>0</v>
       </c>
@@ -85152,7 +84957,7 @@
       </c>
       <c r="AM485" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN485" t="b">
@@ -85554,7 +85359,7 @@
       </c>
       <c r="AM487" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN487" t="b">
@@ -85956,7 +85761,7 @@
       </c>
       <c r="AM489" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN489" t="b">
@@ -86358,7 +86163,7 @@
       </c>
       <c r="AM491" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN491" t="b">
